--- a/GBDS MAY FILES 2026/INVENTORY COUNT SHEET - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/INVENTORY COUNT SHEET - MAY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8548CCAE-1200-4A3C-A14B-90556392B800}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F28A2D-593B-4C41-B9E3-D20E84D7075C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'05-12-2026'!$A$1:$W$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4859,7 +4859,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
-  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <pageSetup paperSize="14" scale="53" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="24" max="80" man="1"/>
   </colBreaks>

--- a/GBDS MAY FILES 2026/INVENTORY COUNT SHEET - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/INVENTORY COUNT SHEET - MAY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F28A2D-593B-4C41-B9E3-D20E84D7075C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D056702-5DBC-47FA-BBE8-666CE7E9978D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>

--- a/GBDS MAY FILES 2026/INVENTORY COUNT SHEET - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/INVENTORY COUNT SHEET - MAY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D056702-5DBC-47FA-BBE8-666CE7E9978D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E068E39-6784-421C-8E19-1AD40C24F965}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
@@ -4858,7 +4858,7 @@
     <mergeCell ref="U4:U5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageMargins left="0" right="0" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
   <pageSetup paperSize="14" scale="53" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="24" max="80" man="1"/>

--- a/GBDS MAY FILES 2026/INVENTORY COUNT SHEET - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/INVENTORY COUNT SHEET - MAY 2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Work\GBDS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\GBDS\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED0289A6-7699-4A96-8D93-B532E494AA7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BDB2141-9F0F-4BB7-9766-E1DBEAF6672D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="18" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1643,6 +1643,18 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="63" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1675,18 +1687,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2015,21 +2015,21 @@
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="I1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="103"/>
+      <c r="T1" s="103"/>
+      <c r="U1" s="103"/>
     </row>
     <row r="2" spans="1:54">
       <c r="B2" s="5" t="s">
@@ -2040,17 +2040,17 @@
       <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="100" t="s">
+      <c r="C4" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="102"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="106"/>
       <c r="M4" s="54" t="s">
         <v>5</v>
       </c>
@@ -2070,13 +2070,13 @@
         <v>6</v>
       </c>
       <c r="S4" s="4"/>
-      <c r="T4" s="103" t="s">
+      <c r="T4" s="107" t="s">
         <v>9</v>
       </c>
       <c r="U4" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="96" t="s">
         <v>11</v>
       </c>
       <c r="AF4" s="84"/>
@@ -2127,9 +2127,9 @@
       <c r="Q5" s="30"/>
       <c r="R5" s="31"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="104"/>
+      <c r="T5" s="108"/>
       <c r="U5" s="114"/>
-      <c r="V5" s="108"/>
+      <c r="V5" s="97"/>
       <c r="AF5" s="84"/>
       <c r="AG5" s="84"/>
       <c r="AH5" s="84"/>
@@ -4660,17 +4660,17 @@
       <c r="B62" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C62" s="96" t="s">
+      <c r="C62" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="D62" s="97"/>
-      <c r="E62" s="97"/>
-      <c r="F62" s="97"/>
-      <c r="G62" s="97"/>
-      <c r="H62" s="97"/>
-      <c r="I62" s="97"/>
-      <c r="J62" s="97"/>
-      <c r="K62" s="98"/>
+      <c r="D62" s="101"/>
+      <c r="E62" s="101"/>
+      <c r="F62" s="101"/>
+      <c r="G62" s="101"/>
+      <c r="H62" s="101"/>
+      <c r="I62" s="101"/>
+      <c r="J62" s="101"/>
+      <c r="K62" s="102"/>
       <c r="U62" s="80" t="s">
         <v>63</v>
       </c>
@@ -4978,21 +4978,21 @@
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="I1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="103"/>
+      <c r="T1" s="103"/>
+      <c r="U1" s="103"/>
     </row>
     <row r="2" spans="1:54">
       <c r="B2" s="5" t="s">
@@ -5003,17 +5003,17 @@
       <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="100" t="s">
+      <c r="C4" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="102"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="106"/>
       <c r="M4" s="54" t="s">
         <v>5</v>
       </c>
@@ -5033,13 +5033,13 @@
         <v>6</v>
       </c>
       <c r="S4" s="4"/>
-      <c r="T4" s="103" t="s">
+      <c r="T4" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="U4" s="105" t="s">
+      <c r="U4" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="96" t="s">
         <v>11</v>
       </c>
       <c r="AF4" s="84"/>
@@ -5079,10 +5079,10 @@
       <c r="I5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="109" t="s">
+      <c r="J5" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="110"/>
+      <c r="K5" s="99"/>
       <c r="M5" s="8"/>
       <c r="N5" s="57"/>
       <c r="O5" s="9"/>
@@ -5090,9 +5090,9 @@
       <c r="Q5" s="30"/>
       <c r="R5" s="31"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="104"/>
-      <c r="U5" s="106"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="110"/>
+      <c r="V5" s="97"/>
       <c r="AF5" s="84"/>
       <c r="AG5" s="84"/>
       <c r="AH5" s="84"/>
@@ -7798,17 +7798,17 @@
       <c r="B60" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C60" s="96" t="s">
+      <c r="C60" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="97"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="97"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="97"/>
-      <c r="I60" s="97"/>
-      <c r="J60" s="97"/>
-      <c r="K60" s="98"/>
+      <c r="D60" s="101"/>
+      <c r="E60" s="101"/>
+      <c r="F60" s="101"/>
+      <c r="G60" s="101"/>
+      <c r="H60" s="101"/>
+      <c r="I60" s="101"/>
+      <c r="J60" s="101"/>
+      <c r="K60" s="102"/>
       <c r="U60" s="80" t="s">
         <v>63</v>
       </c>
@@ -8116,21 +8116,21 @@
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="I1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="103"/>
+      <c r="T1" s="103"/>
+      <c r="U1" s="103"/>
     </row>
     <row r="2" spans="1:54">
       <c r="B2" s="5" t="s">
@@ -8141,17 +8141,17 @@
       <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="100" t="s">
+      <c r="C4" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="102"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="106"/>
       <c r="M4" s="54" t="s">
         <v>5</v>
       </c>
@@ -8171,13 +8171,13 @@
         <v>6</v>
       </c>
       <c r="S4" s="4"/>
-      <c r="T4" s="103" t="s">
+      <c r="T4" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="U4" s="105" t="s">
+      <c r="U4" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="96" t="s">
         <v>11</v>
       </c>
       <c r="AF4" s="84"/>
@@ -8217,10 +8217,10 @@
       <c r="I5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="109" t="s">
+      <c r="J5" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="110"/>
+      <c r="K5" s="99"/>
       <c r="M5" s="8"/>
       <c r="N5" s="57"/>
       <c r="O5" s="9"/>
@@ -8228,9 +8228,9 @@
       <c r="Q5" s="30"/>
       <c r="R5" s="31"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="104"/>
-      <c r="U5" s="106"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="110"/>
+      <c r="V5" s="97"/>
       <c r="AF5" s="84"/>
       <c r="AG5" s="84"/>
       <c r="AH5" s="84"/>
@@ -10931,17 +10931,17 @@
       <c r="B60" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C60" s="96" t="s">
+      <c r="C60" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="97"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="97"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="97"/>
-      <c r="I60" s="97"/>
-      <c r="J60" s="97"/>
-      <c r="K60" s="98"/>
+      <c r="D60" s="101"/>
+      <c r="E60" s="101"/>
+      <c r="F60" s="101"/>
+      <c r="G60" s="101"/>
+      <c r="H60" s="101"/>
+      <c r="I60" s="101"/>
+      <c r="J60" s="101"/>
+      <c r="K60" s="102"/>
       <c r="U60" s="80" t="s">
         <v>63</v>
       </c>
@@ -11250,21 +11250,21 @@
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="I1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="103"/>
+      <c r="T1" s="103"/>
+      <c r="U1" s="103"/>
     </row>
     <row r="2" spans="1:54">
       <c r="B2" s="5" t="s">
@@ -11275,17 +11275,17 @@
       <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="100" t="s">
+      <c r="C4" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="102"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="106"/>
       <c r="M4" s="54" t="s">
         <v>5</v>
       </c>
@@ -11305,13 +11305,13 @@
         <v>6</v>
       </c>
       <c r="S4" s="4"/>
-      <c r="T4" s="103" t="s">
+      <c r="T4" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="U4" s="105" t="s">
+      <c r="U4" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="96" t="s">
         <v>11</v>
       </c>
       <c r="AF4" s="84"/>
@@ -11351,10 +11351,10 @@
       <c r="I5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="109" t="s">
+      <c r="J5" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="110"/>
+      <c r="K5" s="99"/>
       <c r="M5" s="8"/>
       <c r="N5" s="57"/>
       <c r="O5" s="9"/>
@@ -11362,9 +11362,9 @@
       <c r="Q5" s="30"/>
       <c r="R5" s="31"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="104"/>
-      <c r="U5" s="106"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="110"/>
+      <c r="V5" s="97"/>
       <c r="AF5" s="84"/>
       <c r="AG5" s="84"/>
       <c r="AH5" s="84"/>
@@ -14061,17 +14061,17 @@
       <c r="B60" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C60" s="96" t="s">
+      <c r="C60" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="97"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="97"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="97"/>
-      <c r="I60" s="97"/>
-      <c r="J60" s="97"/>
-      <c r="K60" s="98"/>
+      <c r="D60" s="101"/>
+      <c r="E60" s="101"/>
+      <c r="F60" s="101"/>
+      <c r="G60" s="101"/>
+      <c r="H60" s="101"/>
+      <c r="I60" s="101"/>
+      <c r="J60" s="101"/>
+      <c r="K60" s="102"/>
       <c r="U60" s="80" t="s">
         <v>63</v>
       </c>
@@ -14380,21 +14380,21 @@
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="I1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="103"/>
+      <c r="T1" s="103"/>
+      <c r="U1" s="103"/>
     </row>
     <row r="2" spans="1:54">
       <c r="B2" s="5" t="s">
@@ -14405,17 +14405,17 @@
       <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="100" t="s">
+      <c r="C4" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="102"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="106"/>
       <c r="M4" s="54" t="s">
         <v>5</v>
       </c>
@@ -14435,13 +14435,13 @@
         <v>6</v>
       </c>
       <c r="S4" s="4"/>
-      <c r="T4" s="103" t="s">
+      <c r="T4" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="U4" s="105" t="s">
+      <c r="U4" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="96" t="s">
         <v>11</v>
       </c>
       <c r="AF4" s="84"/>
@@ -14481,10 +14481,10 @@
       <c r="I5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="109" t="s">
+      <c r="J5" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="110"/>
+      <c r="K5" s="99"/>
       <c r="M5" s="8"/>
       <c r="N5" s="57"/>
       <c r="O5" s="9"/>
@@ -14492,9 +14492,9 @@
       <c r="Q5" s="30"/>
       <c r="R5" s="31"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="104"/>
-      <c r="U5" s="106"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="110"/>
+      <c r="V5" s="97"/>
       <c r="AF5" s="84"/>
       <c r="AG5" s="84"/>
       <c r="AH5" s="84"/>
@@ -17210,17 +17210,17 @@
       <c r="B60" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C60" s="96" t="s">
+      <c r="C60" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="97"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="97"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="97"/>
-      <c r="I60" s="97"/>
-      <c r="J60" s="97"/>
-      <c r="K60" s="98"/>
+      <c r="D60" s="101"/>
+      <c r="E60" s="101"/>
+      <c r="F60" s="101"/>
+      <c r="G60" s="101"/>
+      <c r="H60" s="101"/>
+      <c r="I60" s="101"/>
+      <c r="J60" s="101"/>
+      <c r="K60" s="102"/>
       <c r="U60" s="80" t="s">
         <v>63</v>
       </c>
@@ -17529,21 +17529,21 @@
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="I1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="103"/>
+      <c r="T1" s="103"/>
+      <c r="U1" s="103"/>
     </row>
     <row r="2" spans="1:54">
       <c r="B2" s="5" t="s">
@@ -17554,17 +17554,17 @@
       <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="100" t="s">
+      <c r="C4" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="102"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="106"/>
       <c r="M4" s="54" t="s">
         <v>5</v>
       </c>
@@ -17584,13 +17584,13 @@
         <v>6</v>
       </c>
       <c r="S4" s="4"/>
-      <c r="T4" s="103" t="s">
+      <c r="T4" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="U4" s="105" t="s">
+      <c r="U4" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="96" t="s">
         <v>11</v>
       </c>
       <c r="AF4" s="84"/>
@@ -17630,10 +17630,10 @@
       <c r="I5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="109" t="s">
+      <c r="J5" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="110"/>
+      <c r="K5" s="99"/>
       <c r="M5" s="8"/>
       <c r="N5" s="57"/>
       <c r="O5" s="9"/>
@@ -17641,9 +17641,9 @@
       <c r="Q5" s="30"/>
       <c r="R5" s="31"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="104"/>
-      <c r="U5" s="106"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="110"/>
+      <c r="V5" s="97"/>
       <c r="AF5" s="84"/>
       <c r="AG5" s="84"/>
       <c r="AH5" s="84"/>
@@ -20352,17 +20352,17 @@
       <c r="B60" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C60" s="96" t="s">
+      <c r="C60" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="97"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="97"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="97"/>
-      <c r="I60" s="97"/>
-      <c r="J60" s="97"/>
-      <c r="K60" s="98"/>
+      <c r="D60" s="101"/>
+      <c r="E60" s="101"/>
+      <c r="F60" s="101"/>
+      <c r="G60" s="101"/>
+      <c r="H60" s="101"/>
+      <c r="I60" s="101"/>
+      <c r="J60" s="101"/>
+      <c r="K60" s="102"/>
       <c r="U60" s="80" t="s">
         <v>63</v>
       </c>
@@ -20670,21 +20670,21 @@
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="I1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="103"/>
+      <c r="T1" s="103"/>
+      <c r="U1" s="103"/>
     </row>
     <row r="2" spans="1:54">
       <c r="B2" s="5" t="s">
@@ -20695,17 +20695,17 @@
       <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="100" t="s">
+      <c r="C4" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="102"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="106"/>
       <c r="M4" s="54" t="s">
         <v>5</v>
       </c>
@@ -20725,13 +20725,13 @@
         <v>6</v>
       </c>
       <c r="S4" s="4"/>
-      <c r="T4" s="103" t="s">
+      <c r="T4" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="U4" s="105" t="s">
+      <c r="U4" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="96" t="s">
         <v>11</v>
       </c>
       <c r="AF4" s="84"/>
@@ -20771,10 +20771,10 @@
       <c r="I5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="109" t="s">
+      <c r="J5" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="110"/>
+      <c r="K5" s="99"/>
       <c r="M5" s="8"/>
       <c r="N5" s="57"/>
       <c r="O5" s="9"/>
@@ -20782,9 +20782,9 @@
       <c r="Q5" s="30"/>
       <c r="R5" s="31"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="104"/>
-      <c r="U5" s="106"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="110"/>
+      <c r="V5" s="97"/>
       <c r="AF5" s="84"/>
       <c r="AG5" s="84"/>
       <c r="AH5" s="84"/>
@@ -23499,17 +23499,17 @@
       <c r="B60" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C60" s="96" t="s">
+      <c r="C60" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="97"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="97"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="97"/>
-      <c r="I60" s="97"/>
-      <c r="J60" s="97"/>
-      <c r="K60" s="98"/>
+      <c r="D60" s="101"/>
+      <c r="E60" s="101"/>
+      <c r="F60" s="101"/>
+      <c r="G60" s="101"/>
+      <c r="H60" s="101"/>
+      <c r="I60" s="101"/>
+      <c r="J60" s="101"/>
+      <c r="K60" s="102"/>
       <c r="U60" s="80" t="s">
         <v>63</v>
       </c>
@@ -23818,21 +23818,21 @@
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="I1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="103"/>
+      <c r="T1" s="103"/>
+      <c r="U1" s="103"/>
     </row>
     <row r="2" spans="1:54">
       <c r="B2" s="5" t="s">
@@ -23843,17 +23843,17 @@
       <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="100" t="s">
+      <c r="C4" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="102"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="106"/>
       <c r="M4" s="54" t="s">
         <v>5</v>
       </c>
@@ -23873,13 +23873,13 @@
         <v>6</v>
       </c>
       <c r="S4" s="4"/>
-      <c r="T4" s="103" t="s">
+      <c r="T4" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="U4" s="105" t="s">
+      <c r="U4" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="96" t="s">
         <v>11</v>
       </c>
       <c r="AF4" s="84"/>
@@ -23919,10 +23919,10 @@
       <c r="I5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="109" t="s">
+      <c r="J5" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="110"/>
+      <c r="K5" s="99"/>
       <c r="M5" s="8"/>
       <c r="N5" s="57"/>
       <c r="O5" s="9"/>
@@ -23930,9 +23930,9 @@
       <c r="Q5" s="30"/>
       <c r="R5" s="31"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="104"/>
-      <c r="U5" s="106"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="110"/>
+      <c r="V5" s="97"/>
       <c r="AF5" s="84"/>
       <c r="AG5" s="84"/>
       <c r="AH5" s="84"/>
@@ -26651,17 +26651,17 @@
       <c r="B60" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C60" s="96" t="s">
+      <c r="C60" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="97"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="97"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="97"/>
-      <c r="I60" s="97"/>
-      <c r="J60" s="97"/>
-      <c r="K60" s="98"/>
+      <c r="D60" s="101"/>
+      <c r="E60" s="101"/>
+      <c r="F60" s="101"/>
+      <c r="G60" s="101"/>
+      <c r="H60" s="101"/>
+      <c r="I60" s="101"/>
+      <c r="J60" s="101"/>
+      <c r="K60" s="102"/>
       <c r="U60" s="80" t="s">
         <v>63</v>
       </c>
@@ -26969,21 +26969,21 @@
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="I1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="103"/>
+      <c r="T1" s="103"/>
+      <c r="U1" s="103"/>
     </row>
     <row r="2" spans="1:54">
       <c r="B2" s="5" t="s">
@@ -26994,17 +26994,17 @@
       <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="100" t="s">
+      <c r="C4" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="102"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="106"/>
       <c r="M4" s="54" t="s">
         <v>5</v>
       </c>
@@ -27024,13 +27024,13 @@
         <v>6</v>
       </c>
       <c r="S4" s="4"/>
-      <c r="T4" s="103" t="s">
+      <c r="T4" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="U4" s="105" t="s">
+      <c r="U4" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="96" t="s">
         <v>11</v>
       </c>
       <c r="AF4" s="84"/>
@@ -27070,10 +27070,10 @@
       <c r="I5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="109" t="s">
+      <c r="J5" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="110"/>
+      <c r="K5" s="99"/>
       <c r="M5" s="8"/>
       <c r="N5" s="57"/>
       <c r="O5" s="9"/>
@@ -27081,9 +27081,9 @@
       <c r="Q5" s="30"/>
       <c r="R5" s="31"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="104"/>
-      <c r="U5" s="106"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="110"/>
+      <c r="V5" s="97"/>
       <c r="AF5" s="84"/>
       <c r="AG5" s="84"/>
       <c r="AH5" s="84"/>
@@ -29811,17 +29811,17 @@
       <c r="B60" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C60" s="96" t="s">
+      <c r="C60" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="97"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="97"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="97"/>
-      <c r="I60" s="97"/>
-      <c r="J60" s="97"/>
-      <c r="K60" s="98"/>
+      <c r="D60" s="101"/>
+      <c r="E60" s="101"/>
+      <c r="F60" s="101"/>
+      <c r="G60" s="101"/>
+      <c r="H60" s="101"/>
+      <c r="I60" s="101"/>
+      <c r="J60" s="101"/>
+      <c r="K60" s="102"/>
       <c r="U60" s="80" t="s">
         <v>63</v>
       </c>
@@ -30129,21 +30129,21 @@
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="I1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="103"/>
+      <c r="T1" s="103"/>
+      <c r="U1" s="103"/>
     </row>
     <row r="2" spans="1:54">
       <c r="B2" s="5" t="s">
@@ -30154,17 +30154,17 @@
       <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="100" t="s">
+      <c r="C4" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="102"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="106"/>
       <c r="M4" s="54" t="s">
         <v>5</v>
       </c>
@@ -30184,13 +30184,13 @@
         <v>6</v>
       </c>
       <c r="S4" s="4"/>
-      <c r="T4" s="103" t="s">
+      <c r="T4" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="U4" s="105" t="s">
+      <c r="U4" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="96" t="s">
         <v>11</v>
       </c>
       <c r="AF4" s="84"/>
@@ -30230,10 +30230,10 @@
       <c r="I5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="109" t="s">
+      <c r="J5" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="110"/>
+      <c r="K5" s="99"/>
       <c r="M5" s="8"/>
       <c r="N5" s="57"/>
       <c r="O5" s="9"/>
@@ -30241,9 +30241,9 @@
       <c r="Q5" s="30"/>
       <c r="R5" s="31"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="104"/>
-      <c r="U5" s="106"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="110"/>
+      <c r="V5" s="97"/>
       <c r="AF5" s="84"/>
       <c r="AG5" s="84"/>
       <c r="AH5" s="84"/>
@@ -32941,17 +32941,17 @@
       <c r="B60" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C60" s="96" t="s">
+      <c r="C60" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="97"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="97"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="97"/>
-      <c r="I60" s="97"/>
-      <c r="J60" s="97"/>
-      <c r="K60" s="98"/>
+      <c r="D60" s="101"/>
+      <c r="E60" s="101"/>
+      <c r="F60" s="101"/>
+      <c r="G60" s="101"/>
+      <c r="H60" s="101"/>
+      <c r="I60" s="101"/>
+      <c r="J60" s="101"/>
+      <c r="K60" s="102"/>
       <c r="U60" s="80" t="s">
         <v>63</v>
       </c>
@@ -33260,21 +33260,21 @@
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="I1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="103"/>
+      <c r="T1" s="103"/>
+      <c r="U1" s="103"/>
     </row>
     <row r="2" spans="1:54">
       <c r="B2" s="5" t="s">
@@ -33285,17 +33285,17 @@
       <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="100" t="s">
+      <c r="C4" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="102"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="106"/>
       <c r="M4" s="54" t="s">
         <v>5</v>
       </c>
@@ -33315,13 +33315,13 @@
         <v>6</v>
       </c>
       <c r="S4" s="4"/>
-      <c r="T4" s="103" t="s">
+      <c r="T4" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="U4" s="105" t="s">
+      <c r="U4" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="96" t="s">
         <v>11</v>
       </c>
       <c r="AF4" s="84"/>
@@ -33361,10 +33361,10 @@
       <c r="I5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="109" t="s">
+      <c r="J5" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="110"/>
+      <c r="K5" s="99"/>
       <c r="M5" s="8"/>
       <c r="N5" s="57"/>
       <c r="O5" s="9"/>
@@ -33372,9 +33372,9 @@
       <c r="Q5" s="30"/>
       <c r="R5" s="31"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="104"/>
-      <c r="U5" s="106"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="110"/>
+      <c r="V5" s="97"/>
       <c r="AF5" s="84"/>
       <c r="AG5" s="84"/>
       <c r="AH5" s="84"/>
@@ -36076,17 +36076,17 @@
       <c r="B60" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C60" s="96" t="s">
+      <c r="C60" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="97"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="97"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="97"/>
-      <c r="I60" s="97"/>
-      <c r="J60" s="97"/>
-      <c r="K60" s="98"/>
+      <c r="D60" s="101"/>
+      <c r="E60" s="101"/>
+      <c r="F60" s="101"/>
+      <c r="G60" s="101"/>
+      <c r="H60" s="101"/>
+      <c r="I60" s="101"/>
+      <c r="J60" s="101"/>
+      <c r="K60" s="102"/>
       <c r="U60" s="80" t="s">
         <v>63</v>
       </c>
@@ -36394,21 +36394,21 @@
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="I1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="103"/>
+      <c r="T1" s="103"/>
+      <c r="U1" s="103"/>
     </row>
     <row r="2" spans="1:54">
       <c r="B2" s="5" t="s">
@@ -36419,17 +36419,17 @@
       <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="100" t="s">
+      <c r="C4" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="102"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="106"/>
       <c r="M4" s="54" t="s">
         <v>5</v>
       </c>
@@ -36449,13 +36449,13 @@
         <v>6</v>
       </c>
       <c r="S4" s="4"/>
-      <c r="T4" s="103" t="s">
+      <c r="T4" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="U4" s="105" t="s">
+      <c r="U4" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="96" t="s">
         <v>11</v>
       </c>
       <c r="AF4" s="84"/>
@@ -36495,10 +36495,10 @@
       <c r="I5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="109" t="s">
+      <c r="J5" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="110"/>
+      <c r="K5" s="99"/>
       <c r="M5" s="8"/>
       <c r="N5" s="57"/>
       <c r="O5" s="9"/>
@@ -36506,9 +36506,9 @@
       <c r="Q5" s="30"/>
       <c r="R5" s="31"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="104"/>
-      <c r="U5" s="106"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="110"/>
+      <c r="V5" s="97"/>
       <c r="AF5" s="84"/>
       <c r="AG5" s="84"/>
       <c r="AH5" s="84"/>
@@ -39221,17 +39221,17 @@
       <c r="B60" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C60" s="96" t="s">
+      <c r="C60" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="97"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="97"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="97"/>
-      <c r="I60" s="97"/>
-      <c r="J60" s="97"/>
-      <c r="K60" s="98"/>
+      <c r="D60" s="101"/>
+      <c r="E60" s="101"/>
+      <c r="F60" s="101"/>
+      <c r="G60" s="101"/>
+      <c r="H60" s="101"/>
+      <c r="I60" s="101"/>
+      <c r="J60" s="101"/>
+      <c r="K60" s="102"/>
       <c r="U60" s="80" t="s">
         <v>63</v>
       </c>
@@ -39540,21 +39540,21 @@
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="I1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="103"/>
+      <c r="T1" s="103"/>
+      <c r="U1" s="103"/>
     </row>
     <row r="2" spans="1:54">
       <c r="B2" s="5" t="s">
@@ -39565,17 +39565,17 @@
       <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="100" t="s">
+      <c r="C4" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="102"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="106"/>
       <c r="M4" s="54" t="s">
         <v>5</v>
       </c>
@@ -39595,13 +39595,13 @@
         <v>6</v>
       </c>
       <c r="S4" s="4"/>
-      <c r="T4" s="103" t="s">
+      <c r="T4" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="U4" s="105" t="s">
+      <c r="U4" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="96" t="s">
         <v>11</v>
       </c>
       <c r="AF4" s="84"/>
@@ -39641,10 +39641,10 @@
       <c r="I5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="109" t="s">
+      <c r="J5" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="110"/>
+      <c r="K5" s="99"/>
       <c r="M5" s="8"/>
       <c r="N5" s="57"/>
       <c r="O5" s="9"/>
@@ -39652,9 +39652,9 @@
       <c r="Q5" s="30"/>
       <c r="R5" s="31"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="104"/>
-      <c r="U5" s="106"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="110"/>
+      <c r="V5" s="97"/>
       <c r="AF5" s="84"/>
       <c r="AG5" s="84"/>
       <c r="AH5" s="84"/>
@@ -42360,17 +42360,17 @@
       <c r="B60" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C60" s="96" t="s">
+      <c r="C60" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="97"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="97"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="97"/>
-      <c r="I60" s="97"/>
-      <c r="J60" s="97"/>
-      <c r="K60" s="98"/>
+      <c r="D60" s="101"/>
+      <c r="E60" s="101"/>
+      <c r="F60" s="101"/>
+      <c r="G60" s="101"/>
+      <c r="H60" s="101"/>
+      <c r="I60" s="101"/>
+      <c r="J60" s="101"/>
+      <c r="K60" s="102"/>
       <c r="U60" s="80" t="s">
         <v>63</v>
       </c>
@@ -42679,21 +42679,21 @@
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="I1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="103"/>
+      <c r="T1" s="103"/>
+      <c r="U1" s="103"/>
     </row>
     <row r="2" spans="1:54">
       <c r="B2" s="5" t="s">
@@ -42704,17 +42704,17 @@
       <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="100" t="s">
+      <c r="C4" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="102"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="106"/>
       <c r="M4" s="54" t="s">
         <v>5</v>
       </c>
@@ -42734,13 +42734,13 @@
         <v>6</v>
       </c>
       <c r="S4" s="4"/>
-      <c r="T4" s="103" t="s">
+      <c r="T4" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="U4" s="105" t="s">
+      <c r="U4" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="96" t="s">
         <v>11</v>
       </c>
       <c r="AF4" s="84"/>
@@ -42780,10 +42780,10 @@
       <c r="I5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="109" t="s">
+      <c r="J5" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="110"/>
+      <c r="K5" s="99"/>
       <c r="M5" s="8"/>
       <c r="N5" s="57"/>
       <c r="O5" s="9"/>
@@ -42791,9 +42791,9 @@
       <c r="Q5" s="30"/>
       <c r="R5" s="31"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="104"/>
-      <c r="U5" s="106"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="110"/>
+      <c r="V5" s="97"/>
       <c r="AF5" s="84"/>
       <c r="AG5" s="84"/>
       <c r="AH5" s="84"/>
@@ -45504,17 +45504,17 @@
       <c r="B60" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C60" s="96" t="s">
+      <c r="C60" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="97"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="97"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="97"/>
-      <c r="I60" s="97"/>
-      <c r="J60" s="97"/>
-      <c r="K60" s="98"/>
+      <c r="D60" s="101"/>
+      <c r="E60" s="101"/>
+      <c r="F60" s="101"/>
+      <c r="G60" s="101"/>
+      <c r="H60" s="101"/>
+      <c r="I60" s="101"/>
+      <c r="J60" s="101"/>
+      <c r="K60" s="102"/>
       <c r="U60" s="80" t="s">
         <v>63</v>
       </c>
@@ -45822,21 +45822,21 @@
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="I1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="103"/>
+      <c r="T1" s="103"/>
+      <c r="U1" s="103"/>
     </row>
     <row r="2" spans="1:54">
       <c r="B2" s="5" t="s">
@@ -45847,17 +45847,17 @@
       <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="100" t="s">
+      <c r="C4" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="102"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="106"/>
       <c r="M4" s="54" t="s">
         <v>5</v>
       </c>
@@ -45877,13 +45877,13 @@
         <v>6</v>
       </c>
       <c r="S4" s="4"/>
-      <c r="T4" s="103" t="s">
+      <c r="T4" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="U4" s="105" t="s">
+      <c r="U4" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="96" t="s">
         <v>11</v>
       </c>
       <c r="AF4" s="84"/>
@@ -45923,10 +45923,10 @@
       <c r="I5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="109" t="s">
+      <c r="J5" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="110"/>
+      <c r="K5" s="99"/>
       <c r="M5" s="8"/>
       <c r="N5" s="57"/>
       <c r="O5" s="9"/>
@@ -45934,9 +45934,9 @@
       <c r="Q5" s="30"/>
       <c r="R5" s="31"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="104"/>
-      <c r="U5" s="106"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="110"/>
+      <c r="V5" s="97"/>
       <c r="AF5" s="84"/>
       <c r="AG5" s="84"/>
       <c r="AH5" s="84"/>
@@ -48644,17 +48644,17 @@
       <c r="B60" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C60" s="96" t="s">
+      <c r="C60" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="97"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="97"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="97"/>
-      <c r="I60" s="97"/>
-      <c r="J60" s="97"/>
-      <c r="K60" s="98"/>
+      <c r="D60" s="101"/>
+      <c r="E60" s="101"/>
+      <c r="F60" s="101"/>
+      <c r="G60" s="101"/>
+      <c r="H60" s="101"/>
+      <c r="I60" s="101"/>
+      <c r="J60" s="101"/>
+      <c r="K60" s="102"/>
       <c r="U60" s="80" t="s">
         <v>63</v>
       </c>
@@ -48963,21 +48963,21 @@
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="I1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="103"/>
+      <c r="T1" s="103"/>
+      <c r="U1" s="103"/>
     </row>
     <row r="2" spans="1:54">
       <c r="B2" s="5" t="s">
@@ -48988,17 +48988,17 @@
       <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="100" t="s">
+      <c r="C4" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="102"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="106"/>
       <c r="M4" s="54" t="s">
         <v>5</v>
       </c>
@@ -49018,13 +49018,13 @@
         <v>6</v>
       </c>
       <c r="S4" s="4"/>
-      <c r="T4" s="103" t="s">
+      <c r="T4" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="U4" s="105" t="s">
+      <c r="U4" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="96" t="s">
         <v>11</v>
       </c>
       <c r="AF4" s="84"/>
@@ -49064,10 +49064,10 @@
       <c r="I5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="109" t="s">
+      <c r="J5" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="110"/>
+      <c r="K5" s="99"/>
       <c r="M5" s="8"/>
       <c r="N5" s="57"/>
       <c r="O5" s="9"/>
@@ -49075,9 +49075,9 @@
       <c r="Q5" s="30"/>
       <c r="R5" s="31"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="104"/>
-      <c r="U5" s="106"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="110"/>
+      <c r="V5" s="97"/>
       <c r="AF5" s="84"/>
       <c r="AG5" s="84"/>
       <c r="AH5" s="84"/>
@@ -51793,17 +51793,17 @@
       <c r="B60" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C60" s="96" t="s">
+      <c r="C60" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="97"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="97"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="97"/>
-      <c r="I60" s="97"/>
-      <c r="J60" s="97"/>
-      <c r="K60" s="98"/>
+      <c r="D60" s="101"/>
+      <c r="E60" s="101"/>
+      <c r="F60" s="101"/>
+      <c r="G60" s="101"/>
+      <c r="H60" s="101"/>
+      <c r="I60" s="101"/>
+      <c r="J60" s="101"/>
+      <c r="K60" s="102"/>
       <c r="U60" s="80" t="s">
         <v>63</v>
       </c>
@@ -52111,21 +52111,21 @@
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="I1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="103"/>
+      <c r="T1" s="103"/>
+      <c r="U1" s="103"/>
     </row>
     <row r="2" spans="1:54">
       <c r="B2" s="5" t="s">
@@ -52136,17 +52136,17 @@
       <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="100" t="s">
+      <c r="C4" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="102"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="106"/>
       <c r="M4" s="54" t="s">
         <v>5</v>
       </c>
@@ -52166,13 +52166,13 @@
         <v>6</v>
       </c>
       <c r="S4" s="4"/>
-      <c r="T4" s="103" t="s">
+      <c r="T4" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="U4" s="105" t="s">
+      <c r="U4" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="96" t="s">
         <v>11</v>
       </c>
       <c r="AF4" s="84"/>
@@ -52212,10 +52212,10 @@
       <c r="I5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="109" t="s">
+      <c r="J5" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="110"/>
+      <c r="K5" s="99"/>
       <c r="M5" s="8"/>
       <c r="N5" s="57"/>
       <c r="O5" s="9"/>
@@ -52223,9 +52223,9 @@
       <c r="Q5" s="30"/>
       <c r="R5" s="31"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="104"/>
-      <c r="U5" s="106"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="110"/>
+      <c r="V5" s="97"/>
       <c r="AF5" s="84"/>
       <c r="AG5" s="84"/>
       <c r="AH5" s="84"/>
@@ -54958,17 +54958,17 @@
       <c r="B60" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C60" s="96" t="s">
+      <c r="C60" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="97"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="97"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="97"/>
-      <c r="I60" s="97"/>
-      <c r="J60" s="97"/>
-      <c r="K60" s="98"/>
+      <c r="D60" s="101"/>
+      <c r="E60" s="101"/>
+      <c r="F60" s="101"/>
+      <c r="G60" s="101"/>
+      <c r="H60" s="101"/>
+      <c r="I60" s="101"/>
+      <c r="J60" s="101"/>
+      <c r="K60" s="102"/>
       <c r="U60" s="80" t="s">
         <v>63</v>
       </c>
@@ -55248,7 +55248,7 @@
     <col min="1" max="1" width="4.109375" style="4" customWidth="1"/>
     <col min="2" max="2" width="12.33203125" style="5" customWidth="1"/>
     <col min="3" max="6" width="10" style="4" customWidth="1"/>
-    <col min="7" max="7" width="6.88671875" style="4" customWidth="1"/>
+    <col min="7" max="7" width="7.33203125" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="6.6640625" style="4" customWidth="1"/>
     <col min="10" max="10" width="6.88671875" style="4" customWidth="1"/>
     <col min="11" max="11" width="6.6640625" style="4" customWidth="1"/>
@@ -55276,21 +55276,21 @@
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="I1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="103"/>
+      <c r="T1" s="103"/>
+      <c r="U1" s="103"/>
     </row>
     <row r="2" spans="1:54">
       <c r="B2" s="5" t="s">
@@ -55301,17 +55301,17 @@
       <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="100" t="s">
+      <c r="C4" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="102"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="106"/>
       <c r="M4" s="54" t="s">
         <v>5</v>
       </c>
@@ -55331,13 +55331,13 @@
         <v>6</v>
       </c>
       <c r="S4" s="4"/>
-      <c r="T4" s="103" t="s">
+      <c r="T4" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="U4" s="105" t="s">
+      <c r="U4" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="96" t="s">
         <v>11</v>
       </c>
       <c r="AF4" s="84"/>
@@ -55377,10 +55377,10 @@
       <c r="I5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="109" t="s">
+      <c r="J5" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="110"/>
+      <c r="K5" s="99"/>
       <c r="M5" s="8"/>
       <c r="N5" s="57"/>
       <c r="O5" s="9"/>
@@ -55388,9 +55388,9 @@
       <c r="Q5" s="30"/>
       <c r="R5" s="31"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="104"/>
-      <c r="U5" s="106"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="110"/>
+      <c r="V5" s="97"/>
       <c r="AF5" s="84"/>
       <c r="AG5" s="84"/>
       <c r="AH5" s="84"/>
@@ -55473,28 +55473,40 @@
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
+      <c r="I7" s="11">
+        <v>3</v>
+      </c>
       <c r="J7" s="32"/>
-      <c r="K7" s="33"/>
+      <c r="K7" s="33">
+        <v>6</v>
+      </c>
       <c r="L7" s="34"/>
-      <c r="M7" s="58"/>
-      <c r="N7" s="59"/>
-      <c r="O7" s="11"/>
+      <c r="M7" s="58">
+        <v>2</v>
+      </c>
+      <c r="N7" s="59">
+        <v>22</v>
+      </c>
+      <c r="O7" s="11">
+        <v>1</v>
+      </c>
       <c r="P7" s="32"/>
-      <c r="Q7" s="32"/>
+      <c r="Q7" s="32">
+        <v>1</v>
+      </c>
       <c r="R7" s="33"/>
       <c r="S7" s="34"/>
       <c r="T7" s="69">
         <f t="shared" ref="T7:T41" si="0">H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="U7" s="69">
         <f t="shared" ref="U7:U36" si="1">C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="V7" s="69">
         <f t="shared" ref="V7:V36" si="2">U7/24</f>
-        <v>0</v>
+        <v>5.291666666666667</v>
       </c>
       <c r="W7" s="78"/>
       <c r="AF7" s="85"/>
@@ -55529,7 +55541,10 @@
       <c r="B8" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="13"/>
+      <c r="C8" s="13">
+        <f>3+63</f>
+        <v>66</v>
+      </c>
       <c r="D8" s="13"/>
       <c r="E8" s="13"/>
       <c r="F8" s="13"/>
@@ -55543,7 +55558,9 @@
       <c r="N8" s="61"/>
       <c r="O8" s="20"/>
       <c r="P8" s="45"/>
-      <c r="Q8" s="45"/>
+      <c r="Q8" s="45">
+        <v>2</v>
+      </c>
       <c r="R8" s="46"/>
       <c r="S8" s="37"/>
       <c r="T8" s="70">
@@ -55552,11 +55569,11 @@
       </c>
       <c r="U8" s="72">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1632</v>
       </c>
       <c r="V8" s="72">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="W8" s="78"/>
       <c r="AF8" s="85"/>
@@ -55591,7 +55608,9 @@
       <c r="B9" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="15">
+        <v>6</v>
+      </c>
       <c r="D9" s="15"/>
       <c r="E9" s="15"/>
       <c r="F9" s="15"/>
@@ -55603,7 +55622,9 @@
       <c r="L9" s="34"/>
       <c r="M9" s="62"/>
       <c r="N9" s="63"/>
-      <c r="O9" s="15"/>
+      <c r="O9" s="15">
+        <v>1</v>
+      </c>
       <c r="P9" s="38"/>
       <c r="Q9" s="38"/>
       <c r="R9" s="39"/>
@@ -55614,11 +55635,11 @@
       </c>
       <c r="U9" s="73">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V9" s="73">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W9" s="78"/>
       <c r="AF9" s="85"/>
@@ -55723,7 +55744,9 @@
       <c r="H11" s="15"/>
       <c r="I11" s="15"/>
       <c r="J11" s="38"/>
-      <c r="K11" s="39"/>
+      <c r="K11" s="39">
+        <v>2</v>
+      </c>
       <c r="L11" s="34"/>
       <c r="M11" s="62"/>
       <c r="N11" s="63"/>
@@ -55734,15 +55757,15 @@
       <c r="S11" s="34"/>
       <c r="T11" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" s="69">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V11" s="69">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="AF11" s="85"/>
       <c r="AG11" s="85"/>
@@ -55775,7 +55798,10 @@
       <c r="B12" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="13"/>
+      <c r="C12" s="13">
+        <f>504+1440+360+576+37</f>
+        <v>2917</v>
+      </c>
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
       <c r="F12" s="13"/>
@@ -55785,11 +55811,15 @@
       <c r="J12" s="35"/>
       <c r="K12" s="36"/>
       <c r="L12" s="37"/>
-      <c r="M12" s="60"/>
+      <c r="M12" s="60">
+        <v>3</v>
+      </c>
       <c r="N12" s="61"/>
       <c r="O12" s="20"/>
       <c r="P12" s="45"/>
-      <c r="Q12" s="45"/>
+      <c r="Q12" s="45">
+        <v>10</v>
+      </c>
       <c r="R12" s="46"/>
       <c r="S12" s="37"/>
       <c r="T12" s="72">
@@ -55798,11 +55828,11 @@
       </c>
       <c r="U12" s="72">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>70320</v>
       </c>
       <c r="V12" s="72">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2930</v>
       </c>
       <c r="W12" s="4"/>
       <c r="X12" s="4"/>
@@ -55844,12 +55874,16 @@
       <c r="B13" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="15"/>
+      <c r="C13" s="15">
+        <v>3</v>
+      </c>
       <c r="D13" s="15"/>
       <c r="E13" s="15"/>
       <c r="F13" s="15"/>
       <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
+      <c r="H13" s="15">
+        <v>16</v>
+      </c>
       <c r="I13" s="15"/>
       <c r="J13" s="38"/>
       <c r="K13" s="39"/>
@@ -55863,15 +55897,15 @@
       <c r="S13" s="34"/>
       <c r="T13" s="73">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U13" s="73">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="V13" s="73">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.6666666666666665</v>
       </c>
       <c r="AF13" s="85"/>
       <c r="AG13" s="85"/>
@@ -55905,7 +55939,9 @@
       <c r="B14" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="15"/>
+      <c r="C14" s="15">
+        <v>4</v>
+      </c>
       <c r="D14" s="15"/>
       <c r="E14" s="15"/>
       <c r="F14" s="15"/>
@@ -55928,11 +55964,11 @@
       </c>
       <c r="U14" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V14" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF14" s="85"/>
       <c r="AG14" s="85"/>
@@ -55966,7 +56002,9 @@
       <c r="B15" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="15"/>
+      <c r="C15" s="15">
+        <v>1</v>
+      </c>
       <c r="D15" s="15"/>
       <c r="E15" s="15"/>
       <c r="F15" s="15"/>
@@ -55989,11 +56027,11 @@
       </c>
       <c r="U15" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V15" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF15" s="85"/>
       <c r="AG15" s="85"/>
@@ -56092,7 +56130,10 @@
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
       <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
+      <c r="G17" s="15">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
       <c r="H17" s="15"/>
       <c r="I17" s="15"/>
       <c r="J17" s="38"/>
@@ -56106,16 +56147,16 @@
       <c r="R17" s="39"/>
       <c r="S17" s="34"/>
       <c r="T17" s="69">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>G17+H17+I17+J17+K17+N17+P17+R17</f>
+        <v>72</v>
       </c>
       <c r="U17" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V17" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF17" s="85"/>
       <c r="AG17" s="85"/>
@@ -56167,7 +56208,7 @@
       <c r="R18" s="39"/>
       <c r="S18" s="34"/>
       <c r="T18" s="69">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="T18:T24" si="5">G18+H18+I18+J18+K18+N18+P18+R18</f>
         <v>0</v>
       </c>
       <c r="U18" s="71">
@@ -56209,11 +56250,16 @@
       <c r="B19" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="15"/>
+      <c r="C19" s="15">
+        <v>3</v>
+      </c>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
       <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
+      <c r="G19" s="15">
+        <f>24+20</f>
+        <v>44</v>
+      </c>
       <c r="H19" s="15"/>
       <c r="I19" s="15"/>
       <c r="J19" s="38"/>
@@ -56227,16 +56273,16 @@
       <c r="R19" s="39"/>
       <c r="S19" s="34"/>
       <c r="T19" s="69">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>44</v>
       </c>
       <c r="U19" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="V19" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="AF19" s="85"/>
       <c r="AG19" s="85"/>
@@ -56264,13 +56310,15 @@
     </row>
     <row r="20" spans="1:54">
       <c r="A20" s="6">
-        <f t="shared" ref="A20:A57" si="5">A19+1</f>
+        <f t="shared" ref="A20:A57" si="6">A19+1</f>
         <v>17</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="15"/>
+      <c r="C20" s="15">
+        <v>6</v>
+      </c>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
       <c r="F20" s="15"/>
@@ -56288,16 +56336,16 @@
       <c r="R20" s="39"/>
       <c r="S20" s="34"/>
       <c r="T20" s="69">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U20" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V20" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF20" s="85"/>
       <c r="AG20" s="85"/>
@@ -56325,17 +56373,22 @@
     </row>
     <row r="21" spans="1:54">
       <c r="A21" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="15"/>
+      <c r="C21" s="15">
+        <v>1</v>
+      </c>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
       <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
+      <c r="G21" s="15">
+        <f>24*2</f>
+        <v>48</v>
+      </c>
       <c r="H21" s="15"/>
       <c r="I21" s="15"/>
       <c r="J21" s="38"/>
@@ -56349,16 +56402,16 @@
       <c r="R21" s="39"/>
       <c r="S21" s="34"/>
       <c r="T21" s="69">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>48</v>
       </c>
       <c r="U21" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V21" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF21" s="85"/>
       <c r="AG21" s="85"/>
@@ -56386,19 +56439,23 @@
     </row>
     <row r="22" spans="1:54" s="2" customFormat="1">
       <c r="A22" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>19</v>
       </c>
       <c r="B22" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="15"/>
+      <c r="C22" s="15">
+        <v>1</v>
+      </c>
       <c r="D22" s="15"/>
       <c r="E22" s="15"/>
       <c r="F22" s="15"/>
       <c r="G22" s="15"/>
       <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
+      <c r="I22" s="15">
+        <v>20</v>
+      </c>
       <c r="J22" s="38"/>
       <c r="K22" s="39"/>
       <c r="L22" s="34"/>
@@ -56410,16 +56467,16 @@
       <c r="R22" s="39"/>
       <c r="S22" s="34"/>
       <c r="T22" s="69">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>20</v>
       </c>
       <c r="U22" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="V22" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.8333333333333333</v>
       </c>
       <c r="W22" s="4"/>
       <c r="X22" s="4"/>
@@ -56456,7 +56513,7 @@
     </row>
     <row r="23" spans="1:54" s="2" customFormat="1">
       <c r="A23" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="B23" s="10" t="s">
@@ -56466,7 +56523,10 @@
       <c r="D23" s="15"/>
       <c r="E23" s="15"/>
       <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
+      <c r="G23" s="15">
+        <f>37*24+19</f>
+        <v>907</v>
+      </c>
       <c r="H23" s="15"/>
       <c r="I23" s="15"/>
       <c r="J23" s="38"/>
@@ -56480,16 +56540,16 @@
       <c r="R23" s="39"/>
       <c r="S23" s="34"/>
       <c r="T23" s="69">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>907</v>
       </c>
       <c r="U23" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="V23" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>37.791666666666664</v>
       </c>
       <c r="W23" s="4"/>
       <c r="X23" s="4"/>
@@ -56526,17 +56586,22 @@
     </row>
     <row r="24" spans="1:54">
       <c r="A24" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>21</v>
       </c>
       <c r="B24" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C24" s="15"/>
+      <c r="C24" s="15">
+        <v>6</v>
+      </c>
       <c r="D24" s="15"/>
       <c r="E24" s="15"/>
       <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
+      <c r="G24" s="15">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
       <c r="H24" s="15"/>
       <c r="I24" s="15"/>
       <c r="J24" s="38"/>
@@ -56550,16 +56615,16 @@
       <c r="R24" s="39"/>
       <c r="S24" s="34"/>
       <c r="T24" s="69">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>72</v>
       </c>
       <c r="U24" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="V24" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AF24" s="85"/>
       <c r="AG24" s="85"/>
@@ -56587,40 +56652,49 @@
     </row>
     <row r="25" spans="1:54">
       <c r="A25" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>22</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="15"/>
+      <c r="C25" s="15">
+        <f>63+22</f>
+        <v>85</v>
+      </c>
       <c r="D25" s="15"/>
       <c r="E25" s="15"/>
       <c r="F25" s="15"/>
       <c r="G25" s="15"/>
       <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
+      <c r="I25" s="15">
+        <v>1</v>
+      </c>
       <c r="J25" s="38"/>
       <c r="K25" s="39"/>
       <c r="L25" s="34"/>
-      <c r="M25" s="62"/>
+      <c r="M25" s="62">
+        <v>1</v>
+      </c>
       <c r="N25" s="63"/>
       <c r="O25" s="15"/>
       <c r="P25" s="38"/>
-      <c r="Q25" s="38"/>
+      <c r="Q25" s="38">
+        <v>2</v>
+      </c>
       <c r="R25" s="39"/>
       <c r="S25" s="34"/>
       <c r="T25" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2113</v>
       </c>
       <c r="V25" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>88.041666666666671</v>
       </c>
       <c r="AY25" s="86" t="e">
         <f>#REF!-AY24</f>
@@ -56629,7 +56703,7 @@
     </row>
     <row r="26" spans="1:54" s="2" customFormat="1">
       <c r="A26" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
       <c r="B26" s="10" t="s">
@@ -56676,13 +56750,15 @@
     </row>
     <row r="27" spans="1:54" s="2" customFormat="1">
       <c r="A27" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>24</v>
       </c>
       <c r="B27" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C27" s="15"/>
+      <c r="C27" s="15">
+        <v>2</v>
+      </c>
       <c r="D27" s="15"/>
       <c r="E27" s="15"/>
       <c r="F27" s="15"/>
@@ -56705,11 +56781,11 @@
       </c>
       <c r="U27" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V27" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W27" s="4"/>
       <c r="X27" s="4"/>
@@ -56723,13 +56799,15 @@
     </row>
     <row r="28" spans="1:54" s="2" customFormat="1">
       <c r="A28" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>25</v>
       </c>
       <c r="B28" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C28" s="15"/>
+      <c r="C28" s="15">
+        <v>57</v>
+      </c>
       <c r="D28" s="15"/>
       <c r="E28" s="15"/>
       <c r="F28" s="15"/>
@@ -56743,7 +56821,9 @@
       <c r="N28" s="63"/>
       <c r="O28" s="15"/>
       <c r="P28" s="38"/>
-      <c r="Q28" s="38"/>
+      <c r="Q28" s="38">
+        <v>3</v>
+      </c>
       <c r="R28" s="39"/>
       <c r="S28" s="34"/>
       <c r="T28" s="69">
@@ -56752,11 +56832,11 @@
       </c>
       <c r="U28" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1440</v>
       </c>
       <c r="V28" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="W28" s="4"/>
       <c r="X28" s="4"/>
@@ -56770,19 +56850,23 @@
     </row>
     <row r="29" spans="1:54">
       <c r="A29" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>26</v>
       </c>
       <c r="B29" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C29" s="15"/>
+      <c r="C29" s="15">
+        <v>63</v>
+      </c>
       <c r="D29" s="15"/>
       <c r="E29" s="15"/>
       <c r="F29" s="15"/>
       <c r="G29" s="15"/>
       <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
+      <c r="I29" s="15">
+        <v>5</v>
+      </c>
       <c r="J29" s="38"/>
       <c r="K29" s="39"/>
       <c r="L29" s="34"/>
@@ -56795,20 +56879,20 @@
       <c r="S29" s="34"/>
       <c r="T29" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U29" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1517</v>
       </c>
       <c r="V29" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>63.208333333333336</v>
       </c>
     </row>
     <row r="30" spans="1:54">
       <c r="A30" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>27</v>
       </c>
       <c r="B30" s="10" t="s">
@@ -56846,7 +56930,7 @@
     </row>
     <row r="31" spans="1:54">
       <c r="A31" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>28</v>
       </c>
       <c r="B31" s="10" t="s">
@@ -56884,13 +56968,15 @@
     </row>
     <row r="32" spans="1:54">
       <c r="A32" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>29</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C32" s="15"/>
+      <c r="C32" s="15">
+        <v>1</v>
+      </c>
       <c r="D32" s="15"/>
       <c r="E32" s="15"/>
       <c r="F32" s="15"/>
@@ -56913,22 +56999,24 @@
       </c>
       <c r="U32" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V32" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:23">
       <c r="A33" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C33" s="15"/>
+      <c r="C33" s="15">
+        <v>2</v>
+      </c>
       <c r="D33" s="15"/>
       <c r="E33" s="15"/>
       <c r="F33" s="15"/>
@@ -56951,54 +57039,69 @@
       </c>
       <c r="U33" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V33" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:23">
       <c r="A34" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>31</v>
       </c>
       <c r="B34" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C34" s="15"/>
+      <c r="C34" s="15">
+        <f>7+72</f>
+        <v>79</v>
+      </c>
       <c r="D34" s="15"/>
       <c r="E34" s="15"/>
       <c r="F34" s="15"/>
       <c r="G34" s="15"/>
       <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
+      <c r="I34" s="15">
+        <v>1</v>
+      </c>
       <c r="J34" s="38"/>
-      <c r="K34" s="39"/>
+      <c r="K34" s="39">
+        <v>1</v>
+      </c>
       <c r="L34" s="34"/>
-      <c r="M34" s="62"/>
+      <c r="M34" s="62">
+        <v>2</v>
+      </c>
       <c r="N34" s="63"/>
-      <c r="O34" s="15"/>
-      <c r="P34" s="38"/>
-      <c r="Q34" s="38"/>
+      <c r="O34" s="15">
+        <v>1</v>
+      </c>
+      <c r="P34" s="38">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="38">
+        <v>8</v>
+      </c>
       <c r="R34" s="39"/>
       <c r="S34" s="34"/>
       <c r="T34" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="U34" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2174</v>
       </c>
       <c r="V34" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>90.583333333333329</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1">
       <c r="A35" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>32</v>
       </c>
       <c r="B35" s="10" t="s">
@@ -57036,13 +57139,15 @@
     </row>
     <row r="36" spans="1:23">
       <c r="A36" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>33</v>
       </c>
       <c r="B36" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="15"/>
+      <c r="C36" s="15">
+        <v>1</v>
+      </c>
       <c r="D36" s="15"/>
       <c r="E36" s="15"/>
       <c r="F36" s="15"/>
@@ -57065,55 +57170,70 @@
       </c>
       <c r="U36" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V36" s="71">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:23" ht="18.600000000000001" thickBot="1">
       <c r="A37" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>34</v>
       </c>
       <c r="B37" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C37" s="13"/>
+      <c r="C37" s="13">
+        <f>324+3672</f>
+        <v>3996</v>
+      </c>
       <c r="D37" s="13"/>
       <c r="E37" s="13"/>
       <c r="F37" s="13"/>
       <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
+      <c r="H37" s="13">
+        <v>3</v>
+      </c>
+      <c r="I37" s="13">
+        <v>2</v>
+      </c>
       <c r="J37" s="35"/>
-      <c r="K37" s="36"/>
+      <c r="K37" s="36">
+        <v>3</v>
+      </c>
       <c r="L37" s="37"/>
-      <c r="M37" s="60"/>
+      <c r="M37" s="60">
+        <v>4</v>
+      </c>
       <c r="N37" s="61"/>
-      <c r="O37" s="20"/>
+      <c r="O37" s="20">
+        <v>40</v>
+      </c>
       <c r="P37" s="45"/>
-      <c r="Q37" s="45"/>
+      <c r="Q37" s="45">
+        <v>28</v>
+      </c>
       <c r="R37" s="46"/>
       <c r="S37" s="37"/>
       <c r="T37" s="74">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U37" s="74">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>24416</v>
       </c>
       <c r="V37" s="74">
         <f>U37/6</f>
-        <v>0</v>
+        <v>4069.3333333333335</v>
       </c>
       <c r="W37" s="78"/>
     </row>
     <row r="38" spans="1:23">
       <c r="A38" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>35</v>
       </c>
       <c r="B38" s="14" t="s">
@@ -57141,17 +57261,17 @@
         <v>0</v>
       </c>
       <c r="U38" s="71">
-        <f t="shared" ref="U38:U40" si="6">C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <f t="shared" ref="U38:U40" si="7">C38*24+M38*24+O38*24+Q38*24+T38</f>
         <v>0</v>
       </c>
       <c r="V38" s="71">
-        <f t="shared" ref="V38:V40" si="7">U38/24</f>
+        <f t="shared" ref="V38:V40" si="8">U38/24</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:23">
       <c r="A39" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>36</v>
       </c>
       <c r="B39" s="16" t="s">
@@ -57179,23 +57299,25 @@
         <v>0</v>
       </c>
       <c r="U39" s="71">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V39" s="71">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:23" ht="18.600000000000001" thickBot="1">
       <c r="A40" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>37</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C40" s="13"/>
+      <c r="C40" s="13">
+        <v>29</v>
+      </c>
       <c r="D40" s="13"/>
       <c r="E40" s="13"/>
       <c r="F40" s="13"/>
@@ -57203,37 +57325,46 @@
       <c r="H40" s="13"/>
       <c r="I40" s="13"/>
       <c r="J40" s="35"/>
-      <c r="K40" s="36"/>
+      <c r="K40" s="36">
+        <v>20</v>
+      </c>
       <c r="L40" s="37"/>
-      <c r="M40" s="60"/>
+      <c r="M40" s="60">
+        <v>1</v>
+      </c>
       <c r="N40" s="61"/>
       <c r="O40" s="20"/>
-      <c r="P40" s="45"/>
+      <c r="P40" s="45">
+        <v>12</v>
+      </c>
       <c r="Q40" s="45"/>
       <c r="R40" s="46"/>
       <c r="S40" s="37"/>
       <c r="T40" s="74">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="U40" s="74">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>752</v>
       </c>
       <c r="V40" s="74">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>31.333333333333332</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="18.600000000000001" thickBot="1">
       <c r="A41" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>38</v>
       </c>
       <c r="B41" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="C41" s="19"/>
+      <c r="C41" s="19">
+        <f>192+71</f>
+        <v>263</v>
+      </c>
       <c r="D41" s="19"/>
       <c r="E41" s="19"/>
       <c r="F41" s="19"/>
@@ -57247,7 +57378,9 @@
       <c r="N41" s="65"/>
       <c r="O41" s="19"/>
       <c r="P41" s="42"/>
-      <c r="Q41" s="42"/>
+      <c r="Q41" s="42">
+        <v>26</v>
+      </c>
       <c r="R41" s="43"/>
       <c r="S41" s="44"/>
       <c r="T41" s="76">
@@ -57256,16 +57389,16 @@
       </c>
       <c r="U41" s="76">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>3468</v>
       </c>
       <c r="V41" s="76">
         <f>U41/12</f>
-        <v>0</v>
+        <v>289</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1">
       <c r="A42" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>39</v>
       </c>
       <c r="B42" s="14" t="s">
@@ -57294,45 +57427,62 @@
     </row>
     <row r="43" spans="1:23" ht="18.600000000000001" thickBot="1">
       <c r="A43" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>40</v>
       </c>
       <c r="B43" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="C43" s="20"/>
+      <c r="C43" s="20">
+        <f>5184+2268+972+8424+3024+5832+5508</f>
+        <v>31212</v>
+      </c>
       <c r="D43" s="20"/>
       <c r="E43" s="20"/>
       <c r="F43" s="20"/>
       <c r="G43" s="20"/>
       <c r="H43" s="20"/>
-      <c r="I43" s="20"/>
-      <c r="J43" s="45"/>
-      <c r="K43" s="46"/>
+      <c r="I43" s="20">
+        <v>7</v>
+      </c>
+      <c r="J43" s="45">
+        <f>7*6+1</f>
+        <v>43</v>
+      </c>
+      <c r="K43" s="46">
+        <f>69*6+7</f>
+        <v>421</v>
+      </c>
       <c r="L43" s="37"/>
-      <c r="M43" s="60"/>
+      <c r="M43" s="60">
+        <v>40</v>
+      </c>
       <c r="N43" s="61"/>
-      <c r="O43" s="20"/>
+      <c r="O43" s="20">
+        <v>147</v>
+      </c>
       <c r="P43" s="45"/>
-      <c r="Q43" s="45"/>
+      <c r="Q43" s="45">
+        <v>116</v>
+      </c>
       <c r="R43" s="46"/>
       <c r="S43" s="37"/>
       <c r="T43" s="74">
-        <f t="shared" ref="T43:T54" si="8">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <f t="shared" ref="T43:T54" si="9">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>471</v>
       </c>
       <c r="U43" s="74">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>189561</v>
       </c>
       <c r="V43" s="74">
         <f>U43/6</f>
-        <v>0</v>
+        <v>31593.5</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1">
       <c r="A44" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>41</v>
       </c>
       <c r="B44" s="14" t="s">
@@ -57361,7 +57511,7 @@
     </row>
     <row r="45" spans="1:23">
       <c r="A45" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>42</v>
       </c>
       <c r="B45" s="10" t="s">
@@ -57381,25 +57531,27 @@
       <c r="N45" s="63"/>
       <c r="O45" s="15"/>
       <c r="P45" s="38"/>
-      <c r="Q45" s="38"/>
+      <c r="Q45" s="38">
+        <v>1</v>
+      </c>
       <c r="R45" s="39"/>
       <c r="S45" s="34"/>
       <c r="T45" s="71">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U45" s="71">
-        <f t="shared" ref="U45:U50" si="9">C45*24+M45*24+O45*24+Q45*24+T45</f>
-        <v>0</v>
+        <f t="shared" ref="U45:U50" si="10">C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>24</v>
       </c>
       <c r="V45" s="71">
-        <f t="shared" ref="V45:V50" si="10">U45/24</f>
-        <v>0</v>
+        <f t="shared" ref="V45:V50" si="11">U45/24</f>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:23">
       <c r="A46" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>43</v>
       </c>
       <c r="B46" s="10" t="s">
@@ -57423,59 +57575,74 @@
       <c r="R46" s="39"/>
       <c r="S46" s="34"/>
       <c r="T46" s="71">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U46" s="71">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="V46" s="71">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:23" ht="18.600000000000001" thickBot="1">
       <c r="A47" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>44</v>
       </c>
       <c r="B47" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C47" s="20"/>
+      <c r="C47" s="20">
+        <f>432+106+2160+74+22</f>
+        <v>2794</v>
+      </c>
       <c r="D47" s="20"/>
       <c r="E47" s="20"/>
       <c r="F47" s="20"/>
       <c r="G47" s="20"/>
       <c r="H47" s="20"/>
-      <c r="I47" s="20"/>
+      <c r="I47" s="20">
+        <v>2</v>
+      </c>
       <c r="J47" s="45"/>
-      <c r="K47" s="46"/>
+      <c r="K47" s="46">
+        <v>4</v>
+      </c>
       <c r="L47" s="37"/>
       <c r="M47" s="60"/>
       <c r="N47" s="61"/>
-      <c r="O47" s="20"/>
-      <c r="P47" s="45"/>
-      <c r="Q47" s="45"/>
-      <c r="R47" s="46"/>
+      <c r="O47" s="20">
+        <v>5</v>
+      </c>
+      <c r="P47" s="45">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="45">
+        <v>9</v>
+      </c>
+      <c r="R47" s="46">
+        <v>3</v>
+      </c>
       <c r="S47" s="37"/>
       <c r="T47" s="74">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>13</v>
       </c>
       <c r="U47" s="74">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>16861</v>
       </c>
       <c r="V47" s="74">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2810.1666666666665</v>
       </c>
     </row>
     <row r="48" spans="1:23">
       <c r="A48" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>45</v>
       </c>
       <c r="B48" s="14" t="s">
@@ -57487,7 +57654,9 @@
       <c r="F48" s="15"/>
       <c r="G48" s="15"/>
       <c r="H48" s="15"/>
-      <c r="I48" s="15"/>
+      <c r="I48" s="15">
+        <v>24</v>
+      </c>
       <c r="J48" s="38"/>
       <c r="K48" s="39"/>
       <c r="L48" s="34"/>
@@ -57499,27 +57668,29 @@
       <c r="R48" s="39"/>
       <c r="S48" s="34"/>
       <c r="T48" s="71">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>24</v>
       </c>
       <c r="U48" s="71">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>24</v>
       </c>
       <c r="V48" s="71">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22">
       <c r="A49" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>46</v>
       </c>
       <c r="B49" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="C49" s="15"/>
+      <c r="C49" s="15">
+        <v>2</v>
+      </c>
       <c r="D49" s="15"/>
       <c r="E49" s="15"/>
       <c r="F49" s="15"/>
@@ -57537,21 +57708,21 @@
       <c r="R49" s="39"/>
       <c r="S49" s="34"/>
       <c r="T49" s="71">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U49" s="71">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>48</v>
       </c>
       <c r="V49" s="71">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:22">
       <c r="A50" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>47</v>
       </c>
       <c r="B50" s="10" t="s">
@@ -57575,27 +57746,29 @@
       <c r="R50" s="39"/>
       <c r="S50" s="34"/>
       <c r="T50" s="71">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U50" s="71">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="V50" s="71">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:22" ht="18.600000000000001" thickBot="1">
       <c r="A51" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>48</v>
       </c>
       <c r="B51" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="C51" s="20"/>
+      <c r="C51" s="20">
+        <v>34</v>
+      </c>
       <c r="D51" s="20"/>
       <c r="E51" s="20"/>
       <c r="F51" s="20"/>
@@ -57613,27 +57786,29 @@
       <c r="R51" s="46"/>
       <c r="S51" s="37"/>
       <c r="T51" s="74">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U51" s="74">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="74">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22">
       <c r="A52" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>49</v>
       </c>
       <c r="B52" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C52" s="15"/>
+      <c r="C52" s="15">
+        <v>1</v>
+      </c>
       <c r="D52" s="15"/>
       <c r="E52" s="15"/>
       <c r="F52" s="15"/>
@@ -57651,27 +57826,29 @@
       <c r="R52" s="39"/>
       <c r="S52" s="34"/>
       <c r="T52" s="71">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U52" s="71">
-        <f t="shared" ref="U52:U54" si="11">C52*24+M52*24+O52*24+Q52*24+T52</f>
-        <v>0</v>
+        <f t="shared" ref="U52:U54" si="12">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>24</v>
       </c>
       <c r="V52" s="71">
-        <f t="shared" ref="V52:V54" si="12">U52/24</f>
-        <v>0</v>
+        <f t="shared" ref="V52:V54" si="13">U52/24</f>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:22">
       <c r="A53" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>50</v>
       </c>
       <c r="B53" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="C53" s="15"/>
+      <c r="C53" s="15">
+        <v>10</v>
+      </c>
       <c r="D53" s="15"/>
       <c r="E53" s="15"/>
       <c r="F53" s="15"/>
@@ -57689,21 +57866,21 @@
       <c r="R53" s="39"/>
       <c r="S53" s="34"/>
       <c r="T53" s="71">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U53" s="71">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>240</v>
       </c>
       <c r="V53" s="71">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="13"/>
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:22">
       <c r="A54" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>51</v>
       </c>
       <c r="B54" s="10"/>
@@ -57725,21 +57902,21 @@
       <c r="R54" s="39"/>
       <c r="S54" s="34"/>
       <c r="T54" s="71">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U54" s="71">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="V54" s="71">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:22">
       <c r="A55" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>52</v>
       </c>
       <c r="B55" s="10"/>
@@ -57766,7 +57943,7 @@
     </row>
     <row r="56" spans="1:22">
       <c r="A56" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>53</v>
       </c>
       <c r="B56" s="10"/>
@@ -57793,7 +57970,7 @@
     </row>
     <row r="57" spans="1:22">
       <c r="A57" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>54</v>
       </c>
       <c r="B57" s="10"/>
@@ -57823,71 +58000,71 @@
         <v>61</v>
       </c>
       <c r="C58" s="22">
-        <f t="shared" ref="C58:K58" si="13">SUM(C7:C57)</f>
-        <v>0</v>
+        <f t="shared" ref="C58:K58" si="14">SUM(C7:C57)</f>
+        <v>41645</v>
       </c>
       <c r="D58" s="22"/>
       <c r="E58" s="22"/>
       <c r="F58" s="22">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="G58" s="22">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>1143</v>
       </c>
       <c r="H58" s="22">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>19</v>
       </c>
       <c r="I58" s="47">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>65</v>
       </c>
       <c r="J58" s="47">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>43</v>
       </c>
       <c r="K58" s="47">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>457</v>
       </c>
       <c r="M58" s="66">
-        <f t="shared" ref="M58:R58" si="14">SUM(M7:M57)</f>
-        <v>0</v>
+        <f t="shared" ref="M58:R58" si="15">SUM(M7:M57)</f>
+        <v>53</v>
       </c>
       <c r="N58" s="66">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>22</v>
       </c>
       <c r="O58" s="66">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>195</v>
       </c>
       <c r="P58" s="66">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>28</v>
       </c>
       <c r="Q58" s="66">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>206</v>
       </c>
       <c r="R58" s="66">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>3</v>
       </c>
       <c r="S58" s="34"/>
       <c r="T58" s="77">
-        <f t="shared" ref="T58:V58" si="15">SUM(T7:T57)</f>
-        <v>0</v>
+        <f t="shared" ref="T58:V58" si="16">SUM(T7:T57)</f>
+        <v>1780</v>
       </c>
       <c r="U58" s="79">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" si="16"/>
+        <v>317038</v>
       </c>
       <c r="V58" s="77">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" si="16"/>
+        <v>42234.666666666664</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1"/>
@@ -57895,17 +58072,17 @@
       <c r="B60" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C60" s="96" t="s">
+      <c r="C60" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="97"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="97"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="97"/>
-      <c r="I60" s="97"/>
-      <c r="J60" s="97"/>
-      <c r="K60" s="98"/>
+      <c r="D60" s="101"/>
+      <c r="E60" s="101"/>
+      <c r="F60" s="101"/>
+      <c r="G60" s="101"/>
+      <c r="H60" s="101"/>
+      <c r="I60" s="101"/>
+      <c r="J60" s="101"/>
+      <c r="K60" s="102"/>
       <c r="U60" s="80" t="s">
         <v>63</v>
       </c>
@@ -58213,21 +58390,21 @@
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="I1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="103"/>
+      <c r="T1" s="103"/>
+      <c r="U1" s="103"/>
     </row>
     <row r="2" spans="1:54">
       <c r="B2" s="5" t="s">
@@ -58238,17 +58415,17 @@
       <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="100" t="s">
+      <c r="C4" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="102"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="106"/>
       <c r="M4" s="54" t="s">
         <v>5</v>
       </c>
@@ -58268,13 +58445,13 @@
         <v>6</v>
       </c>
       <c r="S4" s="4"/>
-      <c r="T4" s="103" t="s">
+      <c r="T4" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="U4" s="105" t="s">
+      <c r="U4" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="96" t="s">
         <v>11</v>
       </c>
       <c r="AF4" s="84"/>
@@ -58314,10 +58491,10 @@
       <c r="I5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="109" t="s">
+      <c r="J5" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="110"/>
+      <c r="K5" s="99"/>
       <c r="M5" s="8"/>
       <c r="N5" s="57"/>
       <c r="O5" s="9"/>
@@ -58325,9 +58502,9 @@
       <c r="Q5" s="30"/>
       <c r="R5" s="31"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="104"/>
-      <c r="U5" s="106"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="110"/>
+      <c r="V5" s="97"/>
       <c r="AF5" s="84"/>
       <c r="AG5" s="84"/>
       <c r="AH5" s="84"/>
@@ -61027,17 +61204,17 @@
       <c r="B60" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C60" s="96" t="s">
+      <c r="C60" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="97"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="97"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="97"/>
-      <c r="I60" s="97"/>
-      <c r="J60" s="97"/>
-      <c r="K60" s="98"/>
+      <c r="D60" s="101"/>
+      <c r="E60" s="101"/>
+      <c r="F60" s="101"/>
+      <c r="G60" s="101"/>
+      <c r="H60" s="101"/>
+      <c r="I60" s="101"/>
+      <c r="J60" s="101"/>
+      <c r="K60" s="102"/>
       <c r="U60" s="80" t="s">
         <v>63</v>
       </c>
@@ -61345,21 +61522,21 @@
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="I1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="103"/>
+      <c r="T1" s="103"/>
+      <c r="U1" s="103"/>
     </row>
     <row r="2" spans="1:54">
       <c r="B2" s="5" t="s">
@@ -61370,17 +61547,17 @@
       <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="100" t="s">
+      <c r="C4" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="102"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="106"/>
       <c r="M4" s="54" t="s">
         <v>5</v>
       </c>
@@ -61400,13 +61577,13 @@
         <v>6</v>
       </c>
       <c r="S4" s="4"/>
-      <c r="T4" s="103" t="s">
+      <c r="T4" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="U4" s="105" t="s">
+      <c r="U4" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="96" t="s">
         <v>11</v>
       </c>
       <c r="AF4" s="84"/>
@@ -61446,10 +61623,10 @@
       <c r="I5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="109" t="s">
+      <c r="J5" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="110"/>
+      <c r="K5" s="99"/>
       <c r="M5" s="8"/>
       <c r="N5" s="57"/>
       <c r="O5" s="9"/>
@@ -61457,9 +61634,9 @@
       <c r="Q5" s="30"/>
       <c r="R5" s="31"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="104"/>
-      <c r="U5" s="106"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="110"/>
+      <c r="V5" s="97"/>
       <c r="AF5" s="84"/>
       <c r="AG5" s="84"/>
       <c r="AH5" s="84"/>
@@ -64173,17 +64350,17 @@
       <c r="B60" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C60" s="96" t="s">
+      <c r="C60" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="97"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="97"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="97"/>
-      <c r="I60" s="97"/>
-      <c r="J60" s="97"/>
-      <c r="K60" s="98"/>
+      <c r="D60" s="101"/>
+      <c r="E60" s="101"/>
+      <c r="F60" s="101"/>
+      <c r="G60" s="101"/>
+      <c r="H60" s="101"/>
+      <c r="I60" s="101"/>
+      <c r="J60" s="101"/>
+      <c r="K60" s="102"/>
       <c r="U60" s="80" t="s">
         <v>63</v>
       </c>
@@ -64491,21 +64668,21 @@
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="I1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="103"/>
+      <c r="T1" s="103"/>
+      <c r="U1" s="103"/>
     </row>
     <row r="2" spans="1:54">
       <c r="B2" s="5" t="s">
@@ -64516,17 +64693,17 @@
       <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="100" t="s">
+      <c r="C4" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="102"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="106"/>
       <c r="M4" s="54" t="s">
         <v>5</v>
       </c>
@@ -64546,13 +64723,13 @@
         <v>6</v>
       </c>
       <c r="S4" s="4"/>
-      <c r="T4" s="103" t="s">
+      <c r="T4" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="U4" s="105" t="s">
+      <c r="U4" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="96" t="s">
         <v>11</v>
       </c>
       <c r="AF4" s="84"/>
@@ -64592,10 +64769,10 @@
       <c r="I5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="109" t="s">
+      <c r="J5" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="110"/>
+      <c r="K5" s="99"/>
       <c r="M5" s="8"/>
       <c r="N5" s="57"/>
       <c r="O5" s="9"/>
@@ -64603,9 +64780,9 @@
       <c r="Q5" s="30"/>
       <c r="R5" s="31"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="104"/>
-      <c r="U5" s="106"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="110"/>
+      <c r="V5" s="97"/>
       <c r="AF5" s="84"/>
       <c r="AG5" s="84"/>
       <c r="AH5" s="84"/>
@@ -67332,17 +67509,17 @@
       <c r="B60" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C60" s="96" t="s">
+      <c r="C60" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="97"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="97"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="97"/>
-      <c r="I60" s="97"/>
-      <c r="J60" s="97"/>
-      <c r="K60" s="98"/>
+      <c r="D60" s="101"/>
+      <c r="E60" s="101"/>
+      <c r="F60" s="101"/>
+      <c r="G60" s="101"/>
+      <c r="H60" s="101"/>
+      <c r="I60" s="101"/>
+      <c r="J60" s="101"/>
+      <c r="K60" s="102"/>
       <c r="U60" s="80" t="s">
         <v>63</v>
       </c>
@@ -67650,21 +67827,21 @@
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="I1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="103"/>
+      <c r="T1" s="103"/>
+      <c r="U1" s="103"/>
     </row>
     <row r="2" spans="1:54">
       <c r="B2" s="5" t="s">
@@ -67675,17 +67852,17 @@
       <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="100" t="s">
+      <c r="C4" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="102"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="106"/>
       <c r="M4" s="54" t="s">
         <v>5</v>
       </c>
@@ -67705,13 +67882,13 @@
         <v>6</v>
       </c>
       <c r="S4" s="4"/>
-      <c r="T4" s="103" t="s">
+      <c r="T4" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="U4" s="105" t="s">
+      <c r="U4" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="96" t="s">
         <v>11</v>
       </c>
       <c r="AF4" s="84"/>
@@ -67751,10 +67928,10 @@
       <c r="I5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="109" t="s">
+      <c r="J5" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="110"/>
+      <c r="K5" s="99"/>
       <c r="M5" s="8"/>
       <c r="N5" s="57"/>
       <c r="O5" s="9"/>
@@ -67762,9 +67939,9 @@
       <c r="Q5" s="30"/>
       <c r="R5" s="31"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="104"/>
-      <c r="U5" s="106"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="110"/>
+      <c r="V5" s="97"/>
       <c r="AF5" s="84"/>
       <c r="AG5" s="84"/>
       <c r="AH5" s="84"/>
@@ -70485,17 +70662,17 @@
       <c r="B60" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C60" s="96" t="s">
+      <c r="C60" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="97"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="97"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="97"/>
-      <c r="I60" s="97"/>
-      <c r="J60" s="97"/>
-      <c r="K60" s="98"/>
+      <c r="D60" s="101"/>
+      <c r="E60" s="101"/>
+      <c r="F60" s="101"/>
+      <c r="G60" s="101"/>
+      <c r="H60" s="101"/>
+      <c r="I60" s="101"/>
+      <c r="J60" s="101"/>
+      <c r="K60" s="102"/>
       <c r="U60" s="80" t="s">
         <v>63</v>
       </c>
@@ -70803,21 +70980,21 @@
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="I1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="103"/>
+      <c r="T1" s="103"/>
+      <c r="U1" s="103"/>
     </row>
     <row r="2" spans="1:54">
       <c r="B2" s="5" t="s">
@@ -70828,17 +71005,17 @@
       <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="100" t="s">
+      <c r="C4" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="102"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="106"/>
       <c r="M4" s="54" t="s">
         <v>5</v>
       </c>
@@ -70858,13 +71035,13 @@
         <v>6</v>
       </c>
       <c r="S4" s="4"/>
-      <c r="T4" s="103" t="s">
+      <c r="T4" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="U4" s="105" t="s">
+      <c r="U4" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="96" t="s">
         <v>11</v>
       </c>
       <c r="AF4" s="84"/>
@@ -70904,10 +71081,10 @@
       <c r="I5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="109" t="s">
+      <c r="J5" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="110"/>
+      <c r="K5" s="99"/>
       <c r="M5" s="8"/>
       <c r="N5" s="57"/>
       <c r="O5" s="9"/>
@@ -70915,9 +71092,9 @@
       <c r="Q5" s="30"/>
       <c r="R5" s="31"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="104"/>
-      <c r="U5" s="106"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="110"/>
+      <c r="V5" s="97"/>
       <c r="AF5" s="84"/>
       <c r="AG5" s="84"/>
       <c r="AH5" s="84"/>
@@ -73619,17 +73796,17 @@
       <c r="B60" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C60" s="96" t="s">
+      <c r="C60" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="97"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="97"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="97"/>
-      <c r="I60" s="97"/>
-      <c r="J60" s="97"/>
-      <c r="K60" s="98"/>
+      <c r="D60" s="101"/>
+      <c r="E60" s="101"/>
+      <c r="F60" s="101"/>
+      <c r="G60" s="101"/>
+      <c r="H60" s="101"/>
+      <c r="I60" s="101"/>
+      <c r="J60" s="101"/>
+      <c r="K60" s="102"/>
       <c r="U60" s="80" t="s">
         <v>63</v>
       </c>
@@ -73938,21 +74115,21 @@
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="I1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="103"/>
+      <c r="T1" s="103"/>
+      <c r="U1" s="103"/>
     </row>
     <row r="2" spans="1:54">
       <c r="B2" s="5" t="s">
@@ -73963,17 +74140,17 @@
       <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="100" t="s">
+      <c r="C4" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="102"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="106"/>
       <c r="M4" s="54" t="s">
         <v>5</v>
       </c>
@@ -73993,13 +74170,13 @@
         <v>6</v>
       </c>
       <c r="S4" s="4"/>
-      <c r="T4" s="103" t="s">
+      <c r="T4" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="U4" s="105" t="s">
+      <c r="U4" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="96" t="s">
         <v>11</v>
       </c>
       <c r="AF4" s="84"/>
@@ -74039,10 +74216,10 @@
       <c r="I5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="109" t="s">
+      <c r="J5" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="110"/>
+      <c r="K5" s="99"/>
       <c r="M5" s="8"/>
       <c r="N5" s="57"/>
       <c r="O5" s="9"/>
@@ -74050,9 +74227,9 @@
       <c r="Q5" s="30"/>
       <c r="R5" s="31"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="104"/>
-      <c r="U5" s="106"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="110"/>
+      <c r="V5" s="97"/>
       <c r="AF5" s="84"/>
       <c r="AG5" s="84"/>
       <c r="AH5" s="84"/>
@@ -76764,17 +76941,17 @@
       <c r="B60" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C60" s="96" t="s">
+      <c r="C60" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="97"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="97"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="97"/>
-      <c r="I60" s="97"/>
-      <c r="J60" s="97"/>
-      <c r="K60" s="98"/>
+      <c r="D60" s="101"/>
+      <c r="E60" s="101"/>
+      <c r="F60" s="101"/>
+      <c r="G60" s="101"/>
+      <c r="H60" s="101"/>
+      <c r="I60" s="101"/>
+      <c r="J60" s="101"/>
+      <c r="K60" s="102"/>
       <c r="U60" s="80" t="s">
         <v>63</v>
       </c>
@@ -77082,21 +77259,21 @@
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="I1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="103"/>
+      <c r="T1" s="103"/>
+      <c r="U1" s="103"/>
     </row>
     <row r="2" spans="1:54">
       <c r="B2" s="5" t="s">
@@ -77107,17 +77284,17 @@
       <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="100" t="s">
+      <c r="C4" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="102"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="106"/>
       <c r="M4" s="54" t="s">
         <v>5</v>
       </c>
@@ -77137,13 +77314,13 @@
         <v>6</v>
       </c>
       <c r="S4" s="4"/>
-      <c r="T4" s="103" t="s">
+      <c r="T4" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="U4" s="105" t="s">
+      <c r="U4" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="96" t="s">
         <v>11</v>
       </c>
       <c r="AF4" s="84"/>
@@ -77183,10 +77360,10 @@
       <c r="I5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="109" t="s">
+      <c r="J5" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="110"/>
+      <c r="K5" s="99"/>
       <c r="M5" s="8"/>
       <c r="N5" s="57"/>
       <c r="O5" s="9"/>
@@ -77194,9 +77371,9 @@
       <c r="Q5" s="30"/>
       <c r="R5" s="31"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="104"/>
-      <c r="U5" s="106"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="110"/>
+      <c r="V5" s="97"/>
       <c r="AF5" s="84"/>
       <c r="AG5" s="84"/>
       <c r="AH5" s="84"/>
@@ -79904,17 +80081,17 @@
       <c r="B60" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C60" s="96" t="s">
+      <c r="C60" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="97"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="97"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="97"/>
-      <c r="I60" s="97"/>
-      <c r="J60" s="97"/>
-      <c r="K60" s="98"/>
+      <c r="D60" s="101"/>
+      <c r="E60" s="101"/>
+      <c r="F60" s="101"/>
+      <c r="G60" s="101"/>
+      <c r="H60" s="101"/>
+      <c r="I60" s="101"/>
+      <c r="J60" s="101"/>
+      <c r="K60" s="102"/>
       <c r="U60" s="80" t="s">
         <v>63</v>
       </c>
